--- a/TestDeliverables.xlsx
+++ b/TestDeliverables.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620" activeTab="3"/>
+    <workbookView windowWidth="20490" windowHeight="7620" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Cover Page" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="68">
   <si>
     <t>Application  Name</t>
   </si>
@@ -130,10 +130,19 @@
     <t>Expected Result</t>
   </si>
   <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Defect ID</t>
+  </si>
+  <si>
     <t>TC_0001</t>
   </si>
   <si>
-    <t>To validate that home page of DocConnect Appplication is displayed</t>
+    <t>To validate that home page of DocConnect Application is displayed</t>
   </si>
   <si>
     <t>Internet,Browser</t>
@@ -150,6 +159,93 @@
     <t>Home page of DocConnect Application should be displayed with following fields
 FirstName
 LastName</t>
+  </si>
+  <si>
+    <t>TC_0002</t>
+  </si>
+  <si>
+    <t>To vaidate the First Name textBox with invalid data</t>
+  </si>
+  <si>
+    <t>FirstName textbox in Find a Doctor page</t>
+  </si>
+  <si>
+    <t>1.Enter "text" in First Name text Box</t>
+  </si>
+  <si>
+    <t>text:12324</t>
+  </si>
+  <si>
+    <t>Error message should be displayed for FirstName text box</t>
+  </si>
+  <si>
+    <t>No error message is displayed for First Name Text Box</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>DF0001</t>
+  </si>
+  <si>
+    <t>Defect Summary</t>
+  </si>
+  <si>
+    <t>Defect Description</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>DF_001</t>
+  </si>
+  <si>
+    <t>User enters Numeric values in the “First-Name” Textbox and the application accepts it</t>
+  </si>
+  <si>
+    <t>Step to Reproduce:
+1. Enter "12232" in First Name textbox
+2. Click on Search Button
+Expected Result : 
+Error message should be displayed for First Name textbox
+Actual Result : 
+No error message is displayed for the First Name text box</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>Requirement Id</t>
+  </si>
+  <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>TS_001</t>
+  </si>
+  <si>
+    <t>TC_001</t>
+  </si>
+  <si>
+    <t>TC_002</t>
+  </si>
+  <si>
+    <t>TC_003</t>
+  </si>
+  <si>
+    <t>TS_002</t>
+  </si>
+  <si>
+    <t>TC_004</t>
   </si>
 </sst>
 </file>
@@ -871,9 +967,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1438,34 +1537,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="2:3">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="2:3">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="2:3">
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="11">
         <v>46259</v>
       </c>
     </row>
@@ -1482,68 +1581,68 @@
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="15.152380952381" customWidth="1"/>
-    <col min="2" max="2" width="33.9619047619048" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.9619047619048" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" ht="60" spans="1:2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="4"/>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="2"/>
-      <c r="B5" s="3"/>
+      <c r="A5" s="3"/>
+      <c r="B5" s="4"/>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="2"/>
-      <c r="B6" s="3"/>
+      <c r="A6" s="3"/>
+      <c r="B6" s="4"/>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="4"/>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
+      <c r="A8" s="3"/>
+      <c r="B8" s="4"/>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="4"/>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="4"/>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3"/>
+      <c r="A11" s="3"/>
+      <c r="B11" s="4"/>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
+      <c r="A12" s="3"/>
+      <c r="B12" s="4"/>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1558,149 +1657,149 @@
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="16.2857142857143" customWidth="1"/>
-    <col min="2" max="2" width="31.2952380952381" style="1" customWidth="1"/>
+    <col min="2" max="2" width="31.2952380952381" style="2" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="2"/>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" ht="30" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="2"/>
+      <c r="C3" s="3"/>
     </row>
     <row r="4" ht="30" spans="1:3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="2"/>
+      <c r="C4" s="3"/>
     </row>
     <row r="5" ht="30" spans="1:3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="2"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" ht="30" spans="1:3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="2"/>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" ht="30" spans="1:3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="2"/>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="2"/>
+      <c r="A8" s="3"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="2"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="2"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="2"/>
+      <c r="A11" s="3"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="2"/>
+      <c r="A12" s="3"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="2"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="2"/>
+      <c r="A14" s="3"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="3"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="2"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="2"/>
+      <c r="A15" s="3"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="3"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="2"/>
+      <c r="A16" s="3"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="3"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="2"/>
+      <c r="A17" s="3"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="3"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="2"/>
+      <c r="A18" s="3"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="3"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="2"/>
+      <c r="A19" s="3"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="3"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="2"/>
+      <c r="A20" s="3"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="3"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="2"/>
+      <c r="A21" s="3"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="3"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="2"/>
+      <c r="A22" s="3"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1711,55 +1810,94 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="1" outlineLevelCol="5"/>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="12.8571428571429" customWidth="1"/>
-    <col min="2" max="2" width="28.4285714285714" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.5714285714286" customWidth="1"/>
-    <col min="4" max="4" width="21.2666666666667" customWidth="1"/>
-    <col min="5" max="5" width="9.14285714285714" style="1"/>
-    <col min="6" max="6" width="16.4285714285714" customWidth="1"/>
+    <col min="2" max="2" width="28.4285714285714" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25.5714285714286" style="2" customWidth="1"/>
+    <col min="4" max="4" width="21.2666666666667" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9.14285714285714" style="2"/>
+    <col min="6" max="6" width="19.5714285714286" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.5714285714286" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" ht="120" spans="1:6">
+      <c r="G1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" ht="105" spans="1:9">
       <c r="A2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>37</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" ht="75" spans="1:9">
+      <c r="A3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1771,9 +1909,57 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="1" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="11.8571428571429" customWidth="1"/>
+    <col min="2" max="2" width="41.8571428571429" style="2" customWidth="1"/>
+    <col min="3" max="3" width="29.4285714285714" customWidth="1"/>
+    <col min="4" max="4" width="12.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="14.4285714285714" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" ht="195" spans="1:6">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1782,9 +1968,67 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="4" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="16.1428571428571" customWidth="1"/>
+    <col min="2" max="2" width="16.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="13.5714285714286" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1"/>
+      <c r="C3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1"/>
+      <c r="C4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1"/>
+      <c r="B5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A5"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
